--- a/data/cox_xlsx/NTGNT.CO.xlsx
+++ b/data/cox_xlsx/NTGNT.CO.xlsx
@@ -3424,21 +3424,11 @@
       <c r="I43" s="15"/>
       <c r="J43" s="15"/>
       <c r="K43" s="15"/>
-      <c r="L43" s="17">
-        <v>3.39</v>
-      </c>
-      <c r="M43" s="17">
-        <v>3.55</v>
-      </c>
-      <c r="N43" s="17">
-        <v>15.29</v>
-      </c>
-      <c r="O43" s="17">
-        <v>9.91</v>
-      </c>
-      <c r="P43" s="17">
-        <v>13.22</v>
-      </c>
+      <c r="L43" s="17"/>
+      <c r="M43" s="17"/>
+      <c r="N43" s="17"/>
+      <c r="O43" s="17"/>
+      <c r="P43" s="17"/>
       <c r="Q43" s="15"/>
       <c r="R43" s="15"/>
       <c r="S43" s="15"/>

--- a/data/cox_xlsx/NTGNT.CO.xlsx
+++ b/data/cox_xlsx/NTGNT.CO.xlsx
@@ -12009,13 +12009,28 @@
       <c r="N60" s="15">
         <v>0.0</v>
       </c>
-      <c r="O60" s="15"/>
-      <c r="P60" s="15"/>
-      <c r="Q60" s="15"/>
-      <c r="R60" s="15"/>
-      <c r="S60" s="15"/>
-      <c r="T60" s="15"/>
-      <c r="U60" s="15"/>
+      <c r="O60" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="P60" s="17">
+        <f>SUM(P61:P62)</f>
+        <v>54.53</v>
+      </c>
+      <c r="Q60" s="17">
+        <v>39.26</v>
+      </c>
+      <c r="R60" s="17">
+        <v>42.45</v>
+      </c>
+      <c r="S60" s="17">
+        <v>51.79</v>
+      </c>
+      <c r="T60" s="17">
+        <v>38.8</v>
+      </c>
+      <c r="U60" s="17">
+        <v>39.62</v>
+      </c>
       <c r="V60" s="15"/>
       <c r="W60" s="15"/>
     </row>

--- a/data/cox_xlsx/NTGNT.CO.xlsx
+++ b/data/cox_xlsx/NTGNT.CO.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="454">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -837,7 +837,10 @@
     <t>Mortgage Debt</t>
   </si>
   <si>
-    <t>Financial Liabilities- Interest bearing liabilities</t>
+    <t>Financial Liabilities LT</t>
+  </si>
+  <si>
+    <t>Financial Liabilities- Interest bearing liabilities LT</t>
   </si>
   <si>
     <t>Misc other L/T liabilities</t>
@@ -13349,8 +13352,8 @@
       </c>
     </row>
     <row r="91" ht="15.0" customHeight="1">
-      <c r="A91" s="14" t="s">
-        <v>262</v>
+      <c r="A91" s="27" t="s">
+        <v>272</v>
       </c>
       <c r="B91" s="16">
         <v>2371.26</v>
@@ -13382,8 +13385,8 @@
       <c r="W91" s="15"/>
     </row>
     <row r="92" ht="15.0" customHeight="1">
-      <c r="A92" s="14" t="s">
-        <v>262</v>
+      <c r="A92" s="27" t="s">
+        <v>272</v>
       </c>
       <c r="B92" s="15"/>
       <c r="C92" s="15"/>
@@ -13411,8 +13414,8 @@
       <c r="W92" s="15"/>
     </row>
     <row r="93" ht="15.0" customHeight="1">
-      <c r="A93" s="14" t="s">
-        <v>272</v>
+      <c r="A93" s="27" t="s">
+        <v>273</v>
       </c>
       <c r="B93" s="15"/>
       <c r="C93" s="15"/>
@@ -13543,7 +13546,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B96" s="15"/>
       <c r="C96" s="15"/>
@@ -13576,7 +13579,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B97" s="16">
         <v>120.22</v>
@@ -13631,7 +13634,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B98" s="17">
         <v>53.78</v>
@@ -13682,7 +13685,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B99" s="15"/>
       <c r="C99" s="15"/>
@@ -13719,7 +13722,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="18" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B100" s="20">
         <v>4112.93</v>
@@ -13778,7 +13781,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B101" s="15"/>
       <c r="C101" s="15"/>
@@ -13815,7 +13818,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B102" s="20">
         <v>7553.55</v>
@@ -13886,7 +13889,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B103" s="16">
         <v>716.6</v>
@@ -13957,7 +13960,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B104" s="16">
         <v>1735.34</v>
@@ -14018,7 +14021,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B105" s="15"/>
       <c r="C105" s="15"/>
@@ -14061,7 +14064,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B106" s="22">
         <v>-53.78</v>
@@ -14098,7 +14101,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B107" s="22">
         <v>-14.24</v>
@@ -14137,7 +14140,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B108" s="16">
         <v>1803.36</v>
@@ -14206,7 +14209,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B109" s="15"/>
       <c r="C109" s="15"/>
@@ -14245,7 +14248,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B110" s="15"/>
       <c r="C110" s="15"/>
@@ -14282,7 +14285,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="18" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B111" s="20">
         <v>2451.94</v>
@@ -14394,7 +14397,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="18" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B113" s="20">
         <v>2584.82</v>
@@ -14465,7 +14468,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="18" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B114" s="19">
         <v>10138.37</v>
@@ -14536,7 +14539,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B115" s="17">
         <v>22.65</v>
@@ -14607,7 +14610,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B116" s="17">
         <v>22.18</v>
@@ -14678,7 +14681,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B117" s="17">
         <v>0.47</v>
@@ -14749,7 +14752,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B118" s="17">
         <v>49.04</v>
@@ -14806,7 +14809,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B119" s="16">
         <v>2371.26</v>
@@ -14863,7 +14866,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B120" s="15">
         <v>0.0</v>
@@ -14920,7 +14923,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B121" s="15"/>
       <c r="C121" s="15"/>
@@ -14971,7 +14974,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B122" s="15"/>
       <c r="C122" s="15"/>
@@ -15000,7 +15003,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B123" s="16">
         <v>531.52</v>
@@ -15055,7 +15058,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B124" s="16">
         <v>1072.53</v>
@@ -15110,7 +15113,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B125" s="16">
         <v>395.47</v>
@@ -15149,7 +15152,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B126" s="15"/>
       <c r="C126" s="15"/>
@@ -15198,7 +15201,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B127" s="15"/>
       <c r="C127" s="15"/>
@@ -15241,7 +15244,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B128" s="15"/>
       <c r="C128" s="15"/>
@@ -15280,7 +15283,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B129" s="15"/>
       <c r="C129" s="15"/>
@@ -15319,7 +15322,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B130" s="15"/>
       <c r="C130" s="15"/>
@@ -15348,7 +15351,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B131" s="15"/>
       <c r="C131" s="15"/>
@@ -15387,7 +15390,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B132" s="15"/>
       <c r="C132" s="15"/>
@@ -15426,7 +15429,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B133" s="15"/>
       <c r="C133" s="15"/>
@@ -15457,7 +15460,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B134" s="15"/>
       <c r="C134" s="15"/>
@@ -15490,7 +15493,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B135" s="15"/>
       <c r="C135" s="15"/>
@@ -15519,7 +15522,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B136" s="15"/>
       <c r="C136" s="15"/>
@@ -15556,7 +15559,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B137" s="15"/>
       <c r="C137" s="15"/>
@@ -15593,7 +15596,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B138" s="17">
         <v>1.0</v>
@@ -15664,7 +15667,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B139" s="17">
         <v>22.65</v>
@@ -15735,7 +15738,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B140" s="17">
         <v>0.47</v>
@@ -15806,7 +15809,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B141" s="17">
         <v>22.18</v>
@@ -16755,7 +16758,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -17141,70 +17144,70 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -17280,7 +17283,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -17447,7 +17450,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B21" s="16">
         <v>580.28</v>
@@ -17486,7 +17489,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B22" s="17">
         <v>25.09</v>
@@ -17527,7 +17530,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B23" s="22">
         <v>-67.44</v>
@@ -17568,7 +17571,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -17597,7 +17600,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B25" s="17">
         <v>26.66</v>
@@ -17638,7 +17641,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B26" s="25">
         <v>-119.19</v>
@@ -17679,7 +17682,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B27" s="25">
         <v>-188.2</v>
@@ -17720,7 +17723,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B28" s="25">
         <v>-211.72</v>
@@ -17761,7 +17764,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -17806,7 +17809,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B30" s="17">
         <v>26.66</v>
@@ -17865,7 +17868,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B31" s="22">
         <v>-67.44</v>
@@ -17926,7 +17929,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -17957,7 +17960,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -18004,7 +18007,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -18047,7 +18050,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -18133,7 +18136,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -18209,7 +18212,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -18264,7 +18267,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B40" s="15"/>
       <c r="C40" s="15"/>
@@ -18303,7 +18306,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -18354,7 +18357,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -18385,7 +18388,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -18418,7 +18421,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -18461,7 +18464,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -18496,7 +18499,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="18" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B46" s="20">
         <v>934.72</v>
@@ -18567,7 +18570,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
@@ -18600,7 +18603,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B48" s="22">
         <v>-64.3</v>
@@ -18657,7 +18660,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B49" s="17">
         <v>42.34</v>
@@ -18714,7 +18717,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B50" s="25">
         <v>-1370.71</v>
@@ -18757,7 +18760,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B51" s="17">
         <v>4.7</v>
@@ -18800,7 +18803,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B52" s="15"/>
       <c r="C52" s="15"/>
@@ -18835,7 +18838,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B53" s="15"/>
       <c r="C53" s="15"/>
@@ -18870,7 +18873,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B54" s="15"/>
       <c r="C54" s="15"/>
@@ -18909,7 +18912,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -18946,7 +18949,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
@@ -18989,7 +18992,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -19038,7 +19041,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B58" s="15"/>
       <c r="C58" s="15"/>
@@ -19069,7 +19072,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
@@ -19100,7 +19103,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B60" s="15"/>
       <c r="C60" s="15"/>
@@ -19135,7 +19138,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
@@ -19172,7 +19175,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
@@ -19201,7 +19204,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="18" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B63" s="24">
         <v>-1387.96</v>
@@ -19272,7 +19275,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
@@ -19305,7 +19308,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B65" s="15"/>
       <c r="C65" s="15"/>
@@ -19348,7 +19351,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
@@ -19379,7 +19382,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B67" s="15"/>
       <c r="C67" s="15"/>
@@ -19410,7 +19413,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B68" s="15"/>
       <c r="C68" s="15"/>
@@ -19461,7 +19464,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B69" s="15"/>
       <c r="C69" s="15"/>
@@ -19494,7 +19497,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B70" s="25">
         <v>-520.68</v>
@@ -19555,7 +19558,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B71" s="16">
         <v>1488.33</v>
@@ -19600,7 +19603,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B72" s="15"/>
       <c r="C72" s="15"/>
@@ -19629,7 +19632,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B73" s="22">
         <v>-58.03</v>
@@ -19670,7 +19673,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B74" s="15"/>
       <c r="C74" s="15">
@@ -19705,7 +19708,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B75" s="22">
         <v>-6.27</v>
@@ -19746,7 +19749,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B76" s="17">
         <v>9.41</v>
@@ -19787,7 +19790,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B77" s="15"/>
       <c r="C77" s="15"/>
@@ -19816,7 +19819,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B78" s="15"/>
       <c r="C78" s="15"/>
@@ -19859,7 +19862,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B79" s="15"/>
       <c r="C79" s="15"/>
@@ -19892,7 +19895,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B80" s="15"/>
       <c r="C80" s="15"/>
@@ -19925,7 +19928,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B81" s="15"/>
       <c r="C81" s="15"/>
@@ -19960,7 +19963,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B82" s="15"/>
       <c r="C82" s="15"/>
@@ -20001,7 +20004,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B83" s="15"/>
       <c r="C83" s="15"/>
@@ -20042,7 +20045,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B84" s="15"/>
       <c r="C84" s="15"/>
@@ -20071,7 +20074,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="18" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B85" s="20">
         <v>912.76</v>
@@ -20142,7 +20145,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B86" s="15"/>
       <c r="C86" s="15"/>
@@ -20173,7 +20176,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="18" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B87" s="19"/>
       <c r="C87" s="19"/>
@@ -20204,7 +20207,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B88" s="16">
         <v>459.52</v>
@@ -20257,7 +20260,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B89" s="22">
         <v>-17.25</v>
@@ -20320,7 +20323,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B90" s="16">
         <v>161.35</v>
@@ -20391,7 +20394,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B91" s="16">
         <v>607.45</v>
@@ -20462,7 +20465,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B92" s="15"/>
       <c r="C92" s="15"/>
@@ -20497,7 +20500,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="18" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B93" s="20">
         <v>442.27</v>
@@ -20568,7 +20571,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B94" s="16">
         <v>464.22</v>
@@ -21534,7 +21537,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -21711,31 +21714,31 @@
         <v>39</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AD11" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AE11" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AF11" s="7" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -22230,7 +22233,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -22335,36 +22338,36 @@
         <v>71</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AA19" s="13" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AC19" s="13" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AD19" s="13" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AE19" s="13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AF19" s="13" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="28" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B20" s="29"/>
       <c r="C20" s="29"/>
@@ -22400,7 +22403,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="30" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B21" s="31">
         <v>10731.26</v>
@@ -22496,7 +22499,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="30" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B22" s="31">
         <v>13102.01</v>
@@ -22584,7 +22587,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="28" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B23" s="29"/>
       <c r="C23" s="29"/>
@@ -22620,7 +22623,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="30" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B24" s="32">
         <v>6786.01</v>
@@ -22716,7 +22719,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="30" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B25" s="31">
         <v>10837.56</v>
@@ -22804,7 +22807,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="28" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B26" s="29"/>
       <c r="C26" s="29"/>
@@ -22840,7 +22843,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="30" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B27" s="32">
         <v>299.61</v>
@@ -22936,7 +22939,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="30" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B28" s="32">
         <v>478.49</v>
@@ -23024,7 +23027,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="28" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B29" s="29"/>
       <c r="C29" s="29"/>
@@ -23060,7 +23063,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="30" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B30" s="35">
         <v>13.4</v>
@@ -23152,7 +23155,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="30" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B31" s="35">
         <v>8.4</v>
@@ -23222,7 +23225,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="28" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B32" s="29"/>
       <c r="C32" s="29"/>
@@ -23258,7 +23261,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="30" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B33" s="33">
         <v>2.71</v>
@@ -23354,7 +23357,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="30" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B34" s="33">
         <v>6.14</v>
@@ -23442,7 +23445,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="28" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B35" s="29"/>
       <c r="C35" s="29"/>
@@ -23478,7 +23481,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="30" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B36" s="31"/>
       <c r="C36" s="31"/>
@@ -23556,7 +23559,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="30" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B37" s="31"/>
       <c r="C37" s="31"/>
@@ -23638,7 +23641,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="28" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B38" s="29"/>
       <c r="C38" s="29"/>
@@ -23674,7 +23677,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="30" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B39" s="33">
         <v>0.36</v>
@@ -23756,7 +23759,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="30" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B40" s="33">
         <v>0.71</v>
@@ -23842,7 +23845,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="28" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B41" s="29"/>
       <c r="C41" s="29"/>
@@ -23878,7 +23881,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="30" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B42" s="33">
         <v>7.46</v>
@@ -23930,7 +23933,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="30" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B43" s="33">
         <v>11.91</v>
@@ -23976,7 +23979,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="28" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B44" s="29"/>
       <c r="C44" s="29"/>
@@ -24012,7 +24015,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="30" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B45" s="33">
         <v>6.6</v>
@@ -24072,7 +24075,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="30" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B46" s="33">
         <v>10.56</v>
@@ -24114,7 +24117,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="28" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B47" s="29"/>
       <c r="C47" s="29"/>
@@ -24150,7 +24153,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="30" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B48" s="33">
         <v>19.08</v>
@@ -24206,7 +24209,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="30" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B49" s="33">
         <v>19.43</v>
@@ -24256,7 +24259,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="28" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B50" s="29"/>
       <c r="C50" s="29"/>
@@ -24292,7 +24295,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="30" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B51" s="33">
         <v>15.99</v>
@@ -24350,7 +24353,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="30" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B52" s="33">
         <v>6.14</v>
@@ -24438,7 +24441,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="28" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B53" s="29"/>
       <c r="C53" s="29"/>
@@ -24474,7 +24477,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="30" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B54" s="34">
         <v>-0.67</v>
@@ -24530,7 +24533,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="30" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B55" s="33">
         <v>1.61</v>
@@ -24570,7 +24573,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="28" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B56" s="29"/>
       <c r="C56" s="29"/>
@@ -24606,7 +24609,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="30" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B57" s="33">
         <v>0.6</v>
@@ -24688,7 +24691,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="30" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B58" s="33">
         <v>0.89</v>
@@ -24774,7 +24777,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="28" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B59" s="29"/>
       <c r="C59" s="29"/>
@@ -24810,7 +24813,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="30" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B60" s="33">
         <v>7.04</v>
@@ -24862,7 +24865,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="30" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B61" s="33">
         <v>9.68</v>
@@ -24916,7 +24919,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="28" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B62" s="29"/>
       <c r="C62" s="29"/>
@@ -24952,7 +24955,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="30" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B63" s="33">
         <v>11.38</v>
@@ -25004,7 +25007,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="30" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B64" s="33">
         <v>14.14</v>
@@ -25054,7 +25057,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="28" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B65" s="29"/>
       <c r="C65" s="29"/>
@@ -25090,7 +25093,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="30" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B66" s="33">
         <v>12.22</v>
@@ -25142,7 +25145,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="30" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B67" s="33">
         <v>14.76</v>
